--- a/outputs/269-44.xlsx
+++ b/outputs/269-44.xlsx
@@ -98,8 +98,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -296,12 +300,12 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>

--- a/outputs/269-44.xlsx
+++ b/outputs/269-44.xlsx
@@ -20,9 +20,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t xml:space="preserve">Chassis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022/04/22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - BWE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X2 -BR2</t>
   </si>
 </sst>
 </file>
@@ -296,7 +305,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:A3"/>
+  <dimension ref="A2:A9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -304,9 +313,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
